--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/INDIANA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/INDIANA_2019.xlsx
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C250">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C633">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C634">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C715">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C716">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C747">
